--- a/results/job_matches_2026-09-28.xlsx
+++ b/results/job_matches_2026-09-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,147 +468,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, AWS, Spark, Kafka, SQL, Snowflake, Databricks, GenAI)</t>
+          <t>Data Engineer - West Region</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Hive</t>
+          <t>AWS, Kinesis, Redshift, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d74f91161f0786df</t>
+          <t>https://www.indeed.com/viewjob?jk=2a19bfa35530d300</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, AWS, Spark, Kafka, SQL, Snowflake, Databricks, GenAI)</t>
+          <t>Data Engineer with ETL/ELT pipelines and API integrations</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>DHANU GLOBAL ENTERPRISES, INC.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Hive</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e06db5919f7704</t>
+          <t>https://www.indeed.com/viewjob?jk=f8385d0cbea264ab</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Front End Engineer</t>
+          <t>Reference Data Engineer New</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d8f8c4202abcea</t>
+          <t>https://www.indeed.com/viewjob?jk=a7000b43a0fcbe29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer with ETL/ELT pipelines and API integrations</t>
+          <t>AI/ML Engineer - Consultant/Senior Consultant - (US-CENTRAL)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DHANU GLOBAL ENTERPRISES, INC.</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8385d0cbea264ab</t>
+          <t>https://www.indeed.com/viewjob?jk=df197bbb6fa7ca32</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (AI Platform &amp; Knowledge Library) (Enterprise Platforms Technology)</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,12 +631,327 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c9d136b2b0b4aee</t>
+          <t>https://www.indeed.com/viewjob?jk=20435d9ad597a311</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (DevOps) - Intelligent Foundations and Experiences (IFX)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5197f016f75b35ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04d0e6836ba7d269</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=997a5797f758baff</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f890393388599b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e70c9dd57a7289c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2ba786a466821b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 (Python, Angular)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c43596c71eebc7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82382cea5259933b</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Azure Engineer- Contract</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IT Audit Labs</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Blob Storage, Event Hubs, Hive, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f11094b2b43d335c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-28.xlsx
+++ b/results/job_matches_2026-09-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,152 +468,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer - West Region</t>
+          <t>Data Engineer with ETL/ELT pipelines and API integrations</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>DHANU GLOBAL ENTERPRISES, INC.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a19bfa35530d300</t>
+          <t>https://www.indeed.com/viewjob?jk=f8385d0cbea264ab</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer with ETL/ELT pipelines and API integrations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DHANU GLOBAL ENTERPRISES, INC.</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8385d0cbea264ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff8cf7c0caa031</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reference Data Engineer New</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7000b43a0fcbe29</t>
+          <t>https://www.indeed.com/viewjob?jk=b433e5c3de97183c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Consultant/Senior Consultant - (US-CENTRAL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df197bbb6fa7ca32</t>
+          <t>https://www.indeed.com/viewjob?jk=e2abd9312c38916a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,103 +622,103 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20435d9ad597a311</t>
+          <t>https://www.indeed.com/viewjob?jk=54c9fe751059a090</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (DevOps) - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5197f016f75b35ad</t>
+          <t>https://www.indeed.com/viewjob?jk=519ba6eb81f01ddd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d0e6836ba7d269</t>
+          <t>https://www.indeed.com/viewjob?jk=02e9b1f872b9ca87</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Reference Data Engineer New</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,164 +741,164 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997a5797f758baff</t>
+          <t>https://www.indeed.com/viewjob?jk=a7000b43a0fcbe29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Software Engineer || - Authentication</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, S3, RDS, GCP, Scala, MySQL, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f890393388599b0</t>
+          <t>https://www.indeed.com/viewjob?jk=309ab450891b7cb4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Sr. Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fusable</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e70c9dd57a7289c</t>
+          <t>https://www.indeed.com/viewjob?jk=977bfd594149d9f5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ba786a466821b0</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fadd67c5d6b60a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Python, Angular)</t>
+          <t>Sr. AI/ML Engineer - OptumHealth - Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c43596c71eebc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf3a051000d27864</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,50 +906,365 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82382cea5259933b</t>
+          <t>https://www.indeed.com/viewjob?jk=efab3b52406bee28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20435d9ad597a311</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (DevOps) - Intelligent Foundations and Experiences (IFX)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5197f016f75b35ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04d0e6836ba7d269</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=997a5797f758baff</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f890393388599b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e70c9dd57a7289c</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2ba786a466821b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 (Python, Angular)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c43596c71eebc7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82382cea5259933b</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Senior Azure Engineer- Contract</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>IT Audit Labs</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D24" t="n">
         <v>10.4</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>RDS, Azure, Blob Storage, Event Hubs, Hive, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f11094b2b43d335c</t>
         </is>

--- a/results/job_matches_2026-09-28.xlsx
+++ b/results/job_matches_2026-09-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer with ETL/ELT pipelines and API integrations</t>
+          <t>Data Engineer - West Region</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DHANU GLOBAL ENTERPRISES, INC.</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, Redshift, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8385d0cbea264ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2a19bfa35530d300</t>
         </is>
       </c>
     </row>
@@ -508,20 +508,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Data Factory, Databricks, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff8cf7c0caa031</t>
+          <t>https://www.indeed.com/viewjob?jk=e85738fcb60fb623</t>
         </is>
       </c>
     </row>
@@ -543,20 +543,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Trisura Guarantee Insurance Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b433e5c3de97183c</t>
+          <t>https://www.indeed.com/viewjob?jk=541b5d8a70246d22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - SS&amp;C EVOLV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2abd9312c38916a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1986790d4088685</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c9fe751059a090</t>
+          <t>https://www.indeed.com/viewjob?jk=271619709a30cff7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Full Stack developer-5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=519ba6eb81f01ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=c40bc09f1a3bfee6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Full Stack developer-5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e9b1f872b9ca87</t>
+          <t>https://www.indeed.com/viewjob?jk=a5be589ee17517c7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reference Data Engineer New</t>
+          <t>Java Full Stack developer-5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7000b43a0fcbe29</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4e07503808394b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer || - Authentication</t>
+          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, GCP, Scala, MySQL, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=309ab450891b7cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=5e0f177f03aebbc1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Dev Ops Engineer</t>
+          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fusable</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977bfd594149d9f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e78ec447c6921557</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fadd67c5d6b60a</t>
+          <t>https://www.indeed.com/viewjob?jk=34d121867f08ee42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - OptumHealth - Remote</t>
+          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf3a051000d27864</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd3cf170c956d7d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,357 +916,2282 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efab3b52406bee28</t>
+          <t>https://www.indeed.com/viewjob?jk=12c8ce709821c415</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20435d9ad597a311</t>
+          <t>https://www.indeed.com/viewjob?jk=1850028e14e4bff5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (DevOps) - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Data Engineer with ETL/ELT pipelines and API integrations</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>DHANU GLOBAL ENTERPRISES, INC.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5197f016f75b35ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f8385d0cbea264ab</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Nexzentek</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, API Gateway, IAM, Databricks, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d0e6836ba7d269</t>
+          <t>https://www.indeed.com/viewjob?jk=4aaa9ea40857cff1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997a5797f758baff</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff8cf7c0caa031</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f890393388599b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b433e5c3de97183c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e70c9dd57a7289c</t>
+          <t>https://www.indeed.com/viewjob?jk=e2abd9312c38916a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ba786a466821b0</t>
+          <t>https://www.indeed.com/viewjob?jk=54c9fe751059a090</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Python, Angular)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c43596c71eebc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=519ba6eb81f01ddd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82382cea5259933b</t>
+          <t>https://www.indeed.com/viewjob?jk=02e9b1f872b9ca87</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cushman &amp; Wakefield</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88b6f2a27bb5dca4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b919203f949fd3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a0601bfbb6c8f14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Reference Data Engineer New</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7000b43a0fcbe29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Short Hills, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Hive, Spark, Scala, MySQL, MongoDB, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e6881384140f95a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Cloud Infrastructure, Asset Management</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Thrivent</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a438d2fde07e7f10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=693264dcdef8b708</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Platform Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>First Due</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d3d5d7e53a35fd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Salesforce Developer with python</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0f22a963618e371</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Salesforce Developer with python</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fae70768d6fa1ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer - Consultant/Senior Consultant - (US-CENTRAL)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Slalom Consulting</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, ETL, ELT, MLOps</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df197bbb6fa7ca32</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sr. Azure DevOps and SRE Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Berlin Packaging</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e9b4b58bac9acaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Engineer Remote - w2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>itheroes inc</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f78144b16700d5b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CloudOps Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tyler Technologies</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=638b097bc0875ea2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CloudOps Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tyler Technologies</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Yarmouth, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b98cfef06d7bc8c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CloudOps Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tyler Technologies</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Lakewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ad0487fcf429038</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CloudOps Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tyler Technologies</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41557f01cc587703</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - App Experience</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HiveWatch</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Hive, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9778ba4147d2ed02</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Blue Shield of California</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99a8ea27729acb82</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Java/AWS Cloud Developer- REMOTE -USA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Creative Information Technology India</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Falls Church, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, API Gateway, ECS, RDS, Scala, SQL Server, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48c2ec5d0b11fb86</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Data Engineer - Kalamazoo, MI</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Greenleaf Trust</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Kalamazoo, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82b7f499e3abfee3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL, ELT</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=724b45955d615a29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tysons, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, S3, RDS, Spark, PySpark, Scala, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc1bec11137219f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>OCI Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f2f25853b8a0412</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Fidelity TalentSource</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Splunk, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d5d12e525fc0c4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Sr. Dev Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Fusable</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=977bfd594149d9f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9fadd67c5d6b60a</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sr. AI/ML Engineer - OptumHealth - Remote</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf3a051000d27864</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Blackpoint Cyber</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49a7e3434ede4595</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17e18497d5c7efef</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Columbia Sportswear</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Azure, Snowflake, SQL Server, Data Modeling, Kimball, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80bccfa443129fc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Faegre Drinker Biddle &amp; Reath LLP</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fdb0c320e9d6d0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Data Architect and Integration Specialist</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GE Vernova</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f898ef3036623e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Engineer PA2026Q3JB011</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SS&amp;C</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0b6663fd8d25645</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efab3b52406bee28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ERCOT/Electric Reliability Council of Texas</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Taylor, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Scala, Oracle, PostgreSQL, Power BI, CI/CD, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bd0e00d31627020</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Control-M Support &amp; Maintenance Engineer (L2/L3)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bef360503cbeb7f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20435d9ad597a311</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (DevOps) - Intelligent Foundations and Experiences (IFX)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5197f016f75b35ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04d0e6836ba7d269</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=997a5797f758baff</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f890393388599b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e70c9dd57a7289c</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2ba786a466821b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 (Python, Angular)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c43596c71eebc7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82382cea5259933b</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Cornell University</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ithaca, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f966e76c6499fe1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Youth Villages</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Chesterfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53c44e30d78a1e64</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Taskrabbit</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, dbt, Tableau, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c7814dca29175e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>Senior Azure Engineer- Contract</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>IT Audit Labs</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D73" t="n">
         <v>10.4</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>RDS, Azure, Blob Storage, Event Hubs, Hive, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f11094b2b43d335c</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Financial Risk Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Openbank Deutschland AG</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Tableau, CI/CD, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4df4a2a841265604</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38100b2f7e3761e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bb55e308f3bed84</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7ae5f57c116bd7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Entry-Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Benda Infotech</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58901101639dcbfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EDM Lead Network</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, GitHub Actions, Terraform, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b73505b55ece80fa</t>
         </is>
       </c>
     </row>
